--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>101.32</v>
+        <v>100.64</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>41.23</v>
+        <v>40.5</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.457</v>
+        <v>1.485</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04565000057220459</v>
+        <v>0.04609000205993653</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093224.933300995</v>
+        <v>3093225.086419753</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>41.23</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>127533664</v>
+        <v>125275616</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.85</v>
+        <v>10.66</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>124885304</v>
+        <v>123797416</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.655764</v>
+        <v>9.571650999999999</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>101580056</v>
+        <v>104455344</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.322900000000001</v>
+        <v>8.558484</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>2.859</v>
+        <v>3.925</v>
       </c>
     </row>
     <row r="8">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>4.3</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="9">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.807</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="10">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118195104</v>
+        <v>120250664</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.078946999999999</v>
+        <v>9.236841999999999</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
@@ -1677,11 +1677,11 @@
         <v>111792000</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>9.815951</v>
+        <v>9.467454999999999</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.855</v>
+        <v>2.224</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>100.64</v>
+        <v>100.98</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.485</v>
+        <v>1.493</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04586999893188477</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>123797416</v>
+        <v>124905448</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.571650999999999</v>
+        <v>9.657321</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>6.105</v>
+        <v>5.478</v>
       </c>
     </row>
     <row r="7">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>104455344</v>
+        <v>104908504</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.558484</v>
+        <v>8.379033</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>120250664</v>
+        <v>118195104</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.236841999999999</v>
+        <v>9.078946999999999</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>117930968</v>
+        <v>116914688</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>9.408784000000001</v>
+        <v>9.327702499999999</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>1.103</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="12">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>111792000</v>
+        <v>111808000</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>9.467454999999999</v>

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>100.98</v>
+        <v>93.62</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>40.5</v>
+        <v>42.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.493</v>
+        <v>1.193</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04586999893188477</v>
+        <v>0.04711999893188477</v>
       </c>
     </row>
     <row r="6">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>37172000</v>
+        <v>26107000</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>112713000</v>
+        <v>84678000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.086419753</v>
+        <v>3093225.105386416</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>40.5</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>125275616</v>
+        <v>132080712</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.66</v>
+        <v>11.51</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.21</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>124905448</v>
+        <v>143590240</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.657321</v>
+        <v>9.767759</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>5.478</v>
+        <v>4.297</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>104908504</v>
+        <v>103898800</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>8.379033</v>
+        <v>8.298387999999999</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>3.925</v>
+        <v>3.943</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>101102688</v>
+        <v>100508344</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>9.232101</v>
+        <v>8.850780500000001</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>4.313</v>
+        <v>4.559</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>136671632</v>
+        <v>141924368</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>11.39466</v>
+        <v>9.891088999999999</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.806</v>
+        <v>1.747</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118195104</v>
+        <v>126833112</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.078946999999999</v>
+        <v>9.462915000000001</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>1.176</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>116914688</v>
+        <v>115178536</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>9.327702499999999</v>
+        <v>8.774194</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>1.078</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>111808000</v>
+        <v>125714120</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>9.467454999999999</v>
+        <v>10.64497</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.224</v>
+        <v>2.571</v>
       </c>
     </row>
     <row r="13">
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>108951040</v>
+        <v>111427200</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.282051</v>
+        <v>11.597938</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>2.36</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="15">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>93.62</v>
+        <v>93.3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>42.7</v>
+        <v>43.05</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.193</v>
+        <v>1.167</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04711999893188477</v>
+        <v>0.04734000205993652</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>3093225.105386416</v>
+        <v>3093224.994192799</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>42.7</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>132080712</v>
+        <v>133163336</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.51</v>
+        <v>11.33</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>143590240</v>
+        <v>142706592</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>9.767759</v>
+        <v>9.707649999999999</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.297</v>
+        <v>4.279</v>
       </c>
     </row>
     <row r="7">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>100508344</v>
+        <v>101153272</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>8.850780500000001</v>
+        <v>8.907572999999999</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>4.559</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>141924368</v>
+        <v>143289984</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>9.891088999999999</v>
+        <v>9.888614</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.747</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="10">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>115178536</v>
+        <v>115601984</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>8.774194</v>
+        <v>8.806452</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>125714120</v>
+        <v>125784000</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>10.64497</v>
+        <v>10.6508875</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>2.571</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="13">
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>111427200</v>
+        <v>111304208</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.597938</v>
+        <v>11.550388</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>2.191</v>
+        <v>2.181</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SFDL_research.xlsx
+++ b/app/reports/SFDL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>93.3</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.167</v>
+        <v>1.166</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04734000205993652</v>
+        <v>0.0473799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.279</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="7">
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>101153272</v>
+        <v>100533632</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>8.907572999999999</v>
+        <v>8.853007</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>143289984</v>
+        <v>142572640</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>9.888614</v>
+        <v>9.9375</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>1.735</v>
+        <v>1.758</v>
       </c>
     </row>
     <row r="10">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>115601984</v>
+        <v>115178536</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>8.806452</v>
+        <v>8.745981</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>0.829</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1699,11 +1699,11 @@
         <v>111304208</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>11.550388</v>
+        <v>11.580312</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>2.181</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="15">
